--- a/apps/web/public/templates/ogrenci-aktarim-sablonu.xlsx
+++ b/apps/web/public/templates/ogrenci-aktarim-sablonu.xlsx
@@ -1,24 +1,121 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ogrenciler" sheetId="1" r:id="R67586d55cd8f497b"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aciklama" sheetId="2" r:id="R51220bb302944c83"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secenekler" sheetId="3" r:id="R8e579c66db6e49c3"/>
+    <sheet sheetId="1" name="Ogrenciler" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Aciklama" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Secenekler" state="visible" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+  <si>
+    <t>okul_no</t>
+  </si>
+  <si>
+    <t>ad</t>
+  </si>
+  <si>
+    <t>soyad</t>
+  </si>
+  <si>
+    <t>seviye</t>
+  </si>
+  <si>
+    <t>sinif</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>tc_kimlik_no</t>
+  </si>
+  <si>
+    <t>telefon</t>
+  </si>
+  <si>
+    <t>veli_ad</t>
+  </si>
+  <si>
+    <t>veli_soyad</t>
+  </si>
+  <si>
+    <t>veli_telefon</t>
+  </si>
+  <si>
+    <t>veli_tc_kimlik_no</t>
+  </si>
+  <si>
+    <t>alan</t>
+  </si>
+  <si>
+    <t>aciklama</t>
+  </si>
+  <si>
+    <t>Opsiyonel okul numarası. Aynı kurum içinde tekil tutulur.</t>
+  </si>
+  <si>
+    <t>Zorunlu öğrenci adı.</t>
+  </si>
+  <si>
+    <t>Zorunlu öğrenci soyadı.</t>
+  </si>
+  <si>
+    <t>Opsiyonel seviye adı veya kodu. Sınıf yoksa zorunludur; sınıf varsa onun seviyesiyle eşleşmelidir.</t>
+  </si>
+  <si>
+    <t>Opsiyonel sınıf adı. Örn. 8-A.</t>
+  </si>
+  <si>
+    <t>Opsiyonel öğrenci e-posta adresi.</t>
+  </si>
+  <si>
+    <t>Opsiyonel öğrenci TC kimlik numarası.</t>
+  </si>
+  <si>
+    <t>Opsiyonel öğrenci telefonu.</t>
+  </si>
+  <si>
+    <t>Opsiyonel veli adı. Veli sütunları öğrenciye iletişim kişisi (yasal veli) olarak yazılır; veli hesabı açılmaz.</t>
+  </si>
+  <si>
+    <t>Opsiyonel veli soyadı. Boşsa öğrenci soyadı kullanılır.</t>
+  </si>
+  <si>
+    <t>Opsiyonel veli telefonu. SMS ve duyuru izinleri kapalı gelir; kurum ayrıca açar.</t>
+  </si>
+  <si>
+    <t>Okunmaz ve saklanmaz. Veli hesabı Veliler ekranından açılıp davet edilir.</t>
+  </si>
+  <si>
+    <t>secenek</t>
+  </si>
+  <si>
+    <t>8. Sınıf</t>
+  </si>
+  <si>
+    <t>8-A</t>
+  </si>
+  <si>
+    <t>05550000000</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <name val="Carlito"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -35,23 +132,53 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OgrencilerTable" displayName="OgrencilerTable" ref="A1:L1" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="OgrencilerTable" displayName="OgrencilerTable" ref="A1:L1" totalsRowShown="1" headerRowCount="1">
+  <autoFilter>
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="12">
     <tableColumn id="1" name="okul_no"/>
     <tableColumn id="2" name="ad"/>
@@ -71,7 +198,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AciklamaTable" displayName="AciklamaTable" ref="A1:B13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" name="AciklamaTable" displayName="AciklamaTable" ref="A1:B13" totalsRowShown="1" headerRowCount="1">
+  <autoFilter>
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" name="alan"/>
     <tableColumn id="2" name="aciklama"/>
@@ -81,7 +212,11 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SeceneklerTable" displayName="SeceneklerTable" ref="A1:B4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" name="SeceneklerTable" displayName="SeceneklerTable" ref="A1:B4" totalsRowShown="1" headerRowCount="1">
+  <autoFilter>
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" name="alan"/>
     <tableColumn id="2" name="secenek"/>
@@ -282,233 +417,235 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="8.779999732971191" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="7.329999923706055" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="7.559999942779541" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="6" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="6.889999866485596" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="12.4399995803833" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.109999656677246" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.109999656677246" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="10.779999732971191" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="11.5600004196167" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="15.890000343322754" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="8.779999732971191" customWidth="1"/>
+    <col min="2" max="2" width="4.670000076293945" customWidth="1"/>
+    <col min="3" max="3" width="7.329999923706055" customWidth="1"/>
+    <col min="4" max="4" width="7.559999942779541" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="6.889999866485596" customWidth="1"/>
+    <col min="7" max="7" width="12.4399995803833" customWidth="1"/>
+    <col min="8" max="9" width="8.109999656677246" customWidth="1"/>
+    <col min="10" max="10" width="10.779999732971191" customWidth="1"/>
+    <col min="11" max="11" width="11.5600004196167" customWidth="1"/>
+    <col min="12" max="12" width="15.890000343322754" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="str">
-        <v>okul_no</v>
-      </c>
-      <c r="B1" s="1" t="str">
-        <v>ad</v>
-      </c>
-      <c r="C1" s="1" t="str">
-        <v>soyad</v>
-      </c>
-      <c r="D1" s="1" t="str">
-        <v>seviye</v>
-      </c>
-      <c r="E1" s="1" t="str">
-        <v>sinif</v>
-      </c>
-      <c r="F1" s="1" t="str">
-        <v>email</v>
-      </c>
-      <c r="G1" s="1" t="str">
-        <v>tc_kimlik_no</v>
-      </c>
-      <c r="H1" s="1" t="str">
-        <v>telefon</v>
-      </c>
-      <c r="I1" s="1" t="str">
-        <v>veli_ad</v>
-      </c>
-      <c r="J1" s="1" t="str">
-        <v>veli_soyad</v>
-      </c>
-      <c r="K1" s="1" t="str">
-        <v>veli_telefon</v>
-      </c>
-      <c r="L1" s="1" t="str">
-        <v>veli_tc_kimlik_no</v>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f2ea382dac54c37"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="25.559999465942383" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="100" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="25.559999465942383" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="str">
-        <v>alan</v>
-      </c>
-      <c r="B1" s="1" t="str">
-        <v>aciklama</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>okul_no</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Opsiyonel okul numarası. Aynı kurum içinde tekil tutulur.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ad</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Zorunlu öğrenci adı.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>soyad</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Zorunlu öğrenci soyadı.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>seviye</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Opsiyonel seviye adı veya kodu. Sınıf yoksa zorunludur; sınıf varsa onun seviyesiyle eşleşmelidir.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>sinif</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Opsiyonel sınıf adı. Örn. 8-A.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>email</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Opsiyonel öğrenci e-posta adresi.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>tc_kimlik_no</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Opsiyonel öğrenci TC kimlik numarası.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>telefon</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Opsiyonel öğrenci telefonu.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>veli_ad</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Opsiyonel veli adı.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>veli_soyad</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Opsiyonel veli soyadı.</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>veli_telefon</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Opsiyonel veli telefonu.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>veli_tc_kimlik_no</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Opsiyonel veli TC kimlik numarası. Veli izinleri SMS, duyuru, finans ve destek için otomatik açık gelir.</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c0202f5d56542ea"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="6" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.5600004196167" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="9.5600004196167" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="str">
-        <v>alan</v>
-      </c>
-      <c r="B1" s="1" t="str">
-        <v>secenek</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>seviye</v>
-      </c>
-      <c r="B2" t="str">
-        <v>8. Sınıf</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>sinif</v>
-      </c>
-      <c r="B3" t="str">
-        <v>8-A</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>telefon</v>
-      </c>
-      <c r="B4" t="str">
-        <v>05550000000</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra39983657afe4dca"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>